--- a/docs/templates/test_fixtures/m_combined.xlsx
+++ b/docs/templates/test_fixtures/m_combined.xlsx
@@ -1,45 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Stock" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stock" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+  <si>
+    <t>Master Design</t>
+  </si>
+  <si>
+    <t>BOTTEGA</t>
+  </si>
+  <si>
+    <t>CERA TILES</t>
+  </si>
+  <si>
+    <t>ENNFACE</t>
+  </si>
+  <si>
+    <t>Size</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>Standard</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>Tile Type</t>
+  </si>
+  <si>
+    <t>Pieces/Box</t>
+  </si>
+  <si>
+    <t>Weight (kg)</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
+    <t>Look</t>
+  </si>
+  <si>
+    <t>CLOUD ONYX</t>
+  </si>
+  <si>
+    <t>Bottega Cloud</t>
+  </si>
+  <si>
+    <t>Cera Onyx</t>
+  </si>
+  <si>
+    <t>800x1600</t>
+  </si>
+  <si>
+    <t>Matt</t>
+  </si>
+  <si>
+    <t>PGVT &amp; GVT</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Marble</t>
+  </si>
+  <si>
+    <t>PLAIN KHAKHI</t>
+  </si>
+  <si>
+    <t>Enn Khakhi</t>
+  </si>
+  <si>
+    <t>600x1200</t>
+  </si>
+  <si>
+    <t>Glossy</t>
+  </si>
+  <si>
+    <t>Porcelain</t>
+  </si>
+  <si>
+    <t>Beige</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>DUNE BEIGE</t>
+  </si>
+  <si>
+    <t>Bottega Dune</t>
+  </si>
+  <si>
+    <t>Cera Dune</t>
+  </si>
+  <si>
+    <t>Enn Dune</t>
+  </si>
+  <si>
+    <t>600x600</t>
+  </si>
+  <si>
+    <t>Ceramic</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B4F72"/>
+        <fgColor rgb="FF1B4F72"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,81 +166,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -418,262 +461,172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="13" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Master Design</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>BOTTEGA</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>CERA TILES</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ENNFACE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Premium</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Surface</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Tile Type</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Pieces/Box</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Weight (kg)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Colour</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Look</t>
-        </is>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CLOUD ONYX</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Bottega Cloud</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cera Onyx</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>800x1600</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2">
         <v>252</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>PGVT &amp; GVT</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2">
         <v>3</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>35</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>White</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Marble</t>
-        </is>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PLAIN KHAKHI</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Enn Khakhi</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>600x1200</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>32</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Glossy</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Porcelain</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>24</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Beige</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Wood</t>
-        </is>
+      <c r="L3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DUNE BEIGE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Bottega Dune</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Cera Dune</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Enn Dune</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>600x600</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4">
         <v>100</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>50</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Matt</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Ceramic</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4">
         <v>6</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>18</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Beige</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Marble</t>
-        </is>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/templates/test_fixtures/m_combined.xlsx
+++ b/docs/templates/test_fixtures/m_combined.xlsx
@@ -14,11 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Master Design</t>
   </si>
   <si>
+    <t>cura ceramic</t>
+  </si>
+  <si>
     <t>BOTTEGA</t>
   </si>
   <si>
@@ -28,6 +31,9 @@
     <t>ENNFACE</t>
   </si>
   <si>
+    <t>ZZ JUNKCOL</t>
+  </si>
+  <si>
     <t>Size</t>
   </si>
   <si>
@@ -58,12 +64,18 @@
     <t>CLOUD ONYX</t>
   </si>
   <si>
+    <t>Cura Cloud</t>
+  </si>
+  <si>
     <t>Bottega Cloud</t>
   </si>
   <si>
     <t>Cera Onyx</t>
   </si>
   <si>
+    <t>Junk Cloud</t>
+  </si>
+  <si>
     <t>800x1600</t>
   </si>
   <si>
@@ -101,6 +113,9 @@
   </si>
   <si>
     <t>DUNE BEIGE</t>
+  </si>
+  <si>
+    <t>Cura Dune</t>
   </si>
   <si>
     <t>Bottega Dune</t>
@@ -462,16 +477,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="13" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" customWidth="1"/>
+    <col min="3" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" customWidth="1"/>
+    <col min="14" max="15" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -511,119 +527,134 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
         <v>252</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+      <c r="M2">
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+      <c r="M3">
+        <v>24</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>50</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4">
+        <v>6</v>
+      </c>
+      <c r="M4">
         <v>18</v>
       </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>35</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" t="s">
         <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>24</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4">
-        <v>100</v>
-      </c>
-      <c r="G4">
-        <v>50</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4">
-        <v>6</v>
-      </c>
-      <c r="K4">
-        <v>18</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/docs/templates/test_fixtures/m_combined.xlsx
+++ b/docs/templates/test_fixtures/m_combined.xlsx
@@ -19,7 +19,7 @@
     <t>Master Design</t>
   </si>
   <si>
-    <t>cura ceramic</t>
+    <t>CURA</t>
   </si>
   <si>
     <t>BOTTEGA</t>
@@ -481,8 +481,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="12" width="12.7109375" customWidth="1"/>
+    <col min="2" max="12" width="12.7109375" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" customWidth="1"/>
     <col min="14" max="15" width="12.7109375" customWidth="1"/>
   </cols>
